--- a/Experiments data/K Size/K_Size_Email_Graph.xlsx
+++ b/Experiments data/K Size/K_Size_Email_Graph.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fengw\OneDrive\Documents\GitHub\SISR Script\Experiments data\K Size\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fengw\OneDrive\Documents\GitHub\KaMinPar_Java\Experiments data\K Size\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D62FB723-0477-4B66-A5A6-A41079B36FFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C114C28C-25A1-45BE-9D63-95858797BEA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Edge Cuts" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="50">
   <si>
     <t>Proposed w/PRRP w/o ILP</t>
   </si>
@@ -171,6 +171,21 @@
   </si>
   <si>
     <t>Deep Multilevel, ε = 0</t>
+  </si>
+  <si>
+    <t>K = 2, Graph = Email, Contraction = 70%, Cardinality Sizes = [491, 642] at f = 0.3, CL= 340</t>
+  </si>
+  <si>
+    <t>Deep Multilevel, epislon = 57</t>
+  </si>
+  <si>
+    <t>Deep Multilevel, epislon =22</t>
+  </si>
+  <si>
+    <t>Deep NUGP, ε = 57</t>
+  </si>
+  <si>
+    <t>Deep NUGP, ε= 0.0</t>
   </si>
 </sst>
 </file>
@@ -648,7 +663,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε= 0.0</c:v>
+                  <c:v>Deep NUGP, ε= 0.0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -711,16 +726,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>885.2</c:v>
+                  <c:v>773</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1746.2</c:v>
+                  <c:v>1258.4000000000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2693.8</c:v>
+                  <c:v>1634.6</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2892.6</c:v>
+                  <c:v>2277</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -741,7 +756,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε = 0.05</c:v>
+                  <c:v>Deep NUGP, ε = 57</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -804,16 +819,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>824.2</c:v>
+                  <c:v>761.2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1324.2</c:v>
+                  <c:v>1251</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2254.6</c:v>
+                  <c:v>1583</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2688.6</c:v>
+                  <c:v>2279</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1740,7 +1755,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε= 0.0</c:v>
+                  <c:v>Deep NUGP, ε= 0.0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1797,16 +1812,16 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>-0.25738636363636369</c:v>
+                  <c:v>-9.8011363636363633E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-0.31076414952709802</c:v>
+                  <c:v>5.5397087524395698E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-0.53861092072195582</c:v>
+                  <c:v>6.636965958419011E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-0.29899407221124469</c:v>
+                  <c:v>-2.2543560265852261E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1827,7 +1842,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε = 5</c:v>
+                  <c:v>Deep NUGP, ε = 57</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1884,16 +1899,16 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>-0.17073863636363643</c:v>
+                  <c:v>-8.1250000000000058E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.0051043386878849E-3</c:v>
+                  <c:v>6.0951809037682061E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-0.28775416952250399</c:v>
+                  <c:v>9.5841900845327829E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-0.20738279144961366</c:v>
+                  <c:v>-2.3441710077240802E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2266,7 +2281,7 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>Runtimes!$F$63</c:f>
+              <c:f>Runtimes!$F$54</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2301,7 +2316,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Runtimes!$A$64:$A$67</c:f>
+              <c:f>Runtimes!$A$55:$A$58</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -2322,7 +2337,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Runtimes!$F$64:$F$67</c:f>
+              <c:f>Runtimes!$F$55:$F$58</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -2353,7 +2368,7 @@
           <c:order val="5"/>
           <c:tx>
             <c:strRef>
-              <c:f>Runtimes!$G$63</c:f>
+              <c:f>Runtimes!$G$54</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2388,7 +2403,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Runtimes!$A$64:$A$67</c:f>
+              <c:f>Runtimes!$A$55:$A$58</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -2409,7 +2424,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Runtimes!$G$64:$G$67</c:f>
+              <c:f>Runtimes!$G$55:$G$58</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -2440,11 +2455,11 @@
           <c:order val="6"/>
           <c:tx>
             <c:strRef>
-              <c:f>Runtimes!$H$63</c:f>
+              <c:f>Runtimes!$H$54</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε= 0.0</c:v>
+                  <c:v>Deep NUGP, ε= 0.0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2481,7 +2496,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Runtimes!$A$64:$A$67</c:f>
+              <c:f>Runtimes!$A$55:$A$58</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -2502,21 +2517,21 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Runtimes!$H$64:$H$67</c:f>
+              <c:f>Runtimes!$H$55:$H$58</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.55199999999999994</c:v>
+                  <c:v>0.63260000000000005</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.89839999999999998</c:v>
+                  <c:v>0.85180000000000011</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.4022000000000001</c:v>
+                  <c:v>1.0902000000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.3812000000000002</c:v>
+                  <c:v>1.2802</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2533,11 +2548,11 @@
           <c:order val="7"/>
           <c:tx>
             <c:strRef>
-              <c:f>Runtimes!$I$63</c:f>
+              <c:f>Runtimes!$I$54</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε = 5</c:v>
+                  <c:v>Deep NUGP, ε = 57</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2574,7 +2589,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Runtimes!$A$64:$A$67</c:f>
+              <c:f>Runtimes!$A$55:$A$58</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -2595,21 +2610,21 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Runtimes!$I$64:$I$67</c:f>
+              <c:f>Runtimes!$I$55:$I$58</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.46379999999999999</c:v>
+                  <c:v>0.6624000000000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.88200000000000001</c:v>
+                  <c:v>0.8256</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.1334</c:v>
+                  <c:v>1.1626000000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.5466</c:v>
+                  <c:v>1.3073999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2642,7 +2657,7 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>Runtimes!$B$63</c15:sqref>
+                          <c15:sqref>Runtimes!$B$54</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -2683,7 +2698,7 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>Runtimes!$A$64:$A$67</c15:sqref>
+                          <c15:sqref>Runtimes!$A$55:$A$58</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -2710,7 +2725,7 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>Runtimes!$B$64:$B$67</c15:sqref>
+                          <c15:sqref>Runtimes!$B$55:$B$58</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -2749,7 +2764,7 @@
                     <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>Runtimes!$C$63</c15:sqref>
+                          <c15:sqref>Runtimes!$C$54</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -2790,7 +2805,7 @@
                     <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>Runtimes!$A$64:$A$67</c15:sqref>
+                          <c15:sqref>Runtimes!$A$55:$A$58</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -2817,7 +2832,7 @@
                     <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>Runtimes!$C$64:$C$67</c15:sqref>
+                          <c15:sqref>Runtimes!$C$55:$C$58</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -2856,7 +2871,7 @@
                     <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>Runtimes!$D$63</c15:sqref>
+                          <c15:sqref>Runtimes!$D$54</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -2897,7 +2912,7 @@
                     <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>Runtimes!$A$64:$A$67</c15:sqref>
+                          <c15:sqref>Runtimes!$A$55:$A$58</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -2924,7 +2939,7 @@
                     <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>Runtimes!$D$64:$D$67</c15:sqref>
+                          <c15:sqref>Runtimes!$D$55:$D$58</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -2963,7 +2978,7 @@
                     <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>Runtimes!$E$63</c15:sqref>
+                          <c15:sqref>Runtimes!$E$54</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -3004,7 +3019,7 @@
                     <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>Runtimes!$A$64:$A$67</c15:sqref>
+                          <c15:sqref>Runtimes!$A$55:$A$58</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -3031,7 +3046,7 @@
                     <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>Runtimes!$E$64:$E$67</c15:sqref>
+                          <c15:sqref>Runtimes!$E$55:$E$58</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -3818,13 +3833,13 @@
                 <c:formatCode>0.000%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>1.1893999999999998E-2</c:v>
+                  <c:v>0.10242999999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.2960000000000003E-2</c:v>
+                  <c:v>4.0809999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="2" formatCode="0.00%">
-                  <c:v>2.9137999999999997E-2</c:v>
+                  <c:v>6.0999999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="3" formatCode="0.00%">
                   <c:v>3.8625999999999994E-2</c:v>
@@ -4503,7 +4518,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε= 0</c:v>
+                  <c:v>Deep NUGP, ε= 0.0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4590,7 +4605,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε = 5</c:v>
+                  <c:v>Deep NUGP, ε = 57</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4647,10 +4662,10 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>2.9430000000000001E-2</c:v>
+                  <c:v>0.10124680000000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>8.7414000000000006E-2</c:v>
+                  <c:v>9.5014000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>2.5940000000000001E-2</c:v>
@@ -5404,16 +5419,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>40.6</c:v>
+                  <c:v>19.600000000000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>164.4</c:v>
+                  <c:v>84</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>329.2</c:v>
+                  <c:v>107</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>333.4</c:v>
+                  <c:v>188.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5505,7 +5520,7 @@
                   <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>248</c:v>
+                  <c:v>180.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9650,13 +9665,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1323416</xdr:colOff>
-      <xdr:row>73</xdr:row>
+      <xdr:row>64</xdr:row>
       <xdr:rowOff>136991</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>459441</xdr:colOff>
-      <xdr:row>96</xdr:row>
+      <xdr:row>87</xdr:row>
       <xdr:rowOff>156883</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -10109,7 +10124,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="B2" s="15"/>
       <c r="C2" s="15"/>
@@ -10153,7 +10168,7 @@
         <v>38</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -10179,7 +10194,7 @@
         <v>704</v>
       </c>
       <c r="H5">
-        <v>884</v>
+        <v>795</v>
       </c>
       <c r="I5">
         <v>761</v>
@@ -10208,10 +10223,10 @@
         <v>704</v>
       </c>
       <c r="H6">
-        <v>859</v>
+        <v>771</v>
       </c>
       <c r="I6">
-        <v>958</v>
+        <v>831</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -10237,7 +10252,7 @@
         <v>704</v>
       </c>
       <c r="H7">
-        <v>941</v>
+        <v>757</v>
       </c>
       <c r="I7">
         <v>773</v>
@@ -10266,10 +10281,10 @@
         <v>704</v>
       </c>
       <c r="H8">
-        <v>958</v>
+        <v>758</v>
       </c>
       <c r="I8">
-        <v>904</v>
+        <v>716</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -10352,7 +10367,7 @@
         <v>38</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -10378,10 +10393,10 @@
         <v>1266</v>
       </c>
       <c r="H16">
-        <v>1802</v>
+        <v>1246</v>
       </c>
       <c r="I16">
-        <v>1355</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -10407,10 +10422,10 @@
         <v>1278</v>
       </c>
       <c r="H17">
-        <v>1889</v>
+        <v>1223</v>
       </c>
       <c r="I17">
-        <v>1360</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -10436,10 +10451,10 @@
         <v>1343</v>
       </c>
       <c r="H18">
-        <v>1549</v>
+        <v>1230</v>
       </c>
       <c r="I18">
-        <v>1302</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -10465,7 +10480,7 @@
         <v>1433</v>
       </c>
       <c r="H19">
-        <v>1805</v>
+        <v>1345</v>
       </c>
       <c r="I19">
         <v>1287</v>
@@ -10494,10 +10509,10 @@
         <v>1341</v>
       </c>
       <c r="H20">
-        <v>1686</v>
+        <v>1248</v>
       </c>
       <c r="I20">
-        <v>1317</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -10546,7 +10561,7 @@
         <v>38</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -10572,10 +10587,10 @@
         <v>1717</v>
       </c>
       <c r="H27">
-        <v>2675</v>
+        <v>1640</v>
       </c>
       <c r="I27">
-        <v>2191</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
@@ -10601,10 +10616,10 @@
         <v>1739</v>
       </c>
       <c r="H28">
-        <v>2689</v>
+        <v>1534</v>
       </c>
       <c r="I28">
-        <v>2386</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
@@ -10630,10 +10645,10 @@
         <v>1739</v>
       </c>
       <c r="H29">
-        <v>2508</v>
+        <v>1689</v>
       </c>
       <c r="I29">
-        <v>2161</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -10659,10 +10674,10 @@
         <v>1776</v>
       </c>
       <c r="H30">
-        <v>2793</v>
+        <v>1688</v>
       </c>
       <c r="I30">
-        <v>2203</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -10688,10 +10703,10 @@
         <v>1783</v>
       </c>
       <c r="H31">
-        <v>2804</v>
+        <v>1622</v>
       </c>
       <c r="I31">
-        <v>2332</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
@@ -10766,10 +10781,10 @@
         <v>2189</v>
       </c>
       <c r="H38">
-        <v>2795</v>
+        <v>2290</v>
       </c>
       <c r="I38">
-        <v>2412</v>
+        <v>2329</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
@@ -10795,10 +10810,10 @@
         <v>2229</v>
       </c>
       <c r="H39">
-        <v>2874</v>
+        <v>2622</v>
       </c>
       <c r="I39">
-        <v>2811</v>
+        <v>2278</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -10824,10 +10839,10 @@
         <v>2256</v>
       </c>
       <c r="H40">
-        <v>2738</v>
+        <v>2064</v>
       </c>
       <c r="I40">
-        <v>2810</v>
+        <v>2504</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
@@ -10853,10 +10868,10 @@
         <v>2226</v>
       </c>
       <c r="H41">
-        <v>2947</v>
+        <v>2581</v>
       </c>
       <c r="I41">
-        <v>2683</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -10882,10 +10897,10 @@
         <v>2234</v>
       </c>
       <c r="H42">
-        <v>3109</v>
+        <v>1828</v>
       </c>
       <c r="I42">
-        <v>2727</v>
+        <v>2298</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
@@ -10920,10 +10935,10 @@
         <v>14</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
@@ -10956,11 +10971,11 @@
       </c>
       <c r="H49">
         <f>AVERAGE(H5:H9)</f>
-        <v>885.2</v>
+        <v>773</v>
       </c>
       <c r="I49">
         <f>AVERAGE(I5:I9)</f>
-        <v>824.2</v>
+        <v>761.2</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
@@ -10993,11 +11008,11 @@
       </c>
       <c r="H50">
         <f>AVERAGE(H16:H20)</f>
-        <v>1746.2</v>
+        <v>1258.4000000000001</v>
       </c>
       <c r="I50">
         <f>AVERAGE(I16:I20)</f>
-        <v>1324.2</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
@@ -11030,11 +11045,11 @@
       </c>
       <c r="H51">
         <f>AVERAGE(H27:H31)</f>
-        <v>2693.8</v>
+        <v>1634.6</v>
       </c>
       <c r="I51">
         <f>AVERAGE(I27:I31)</f>
-        <v>2254.6</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
@@ -11067,11 +11082,11 @@
       </c>
       <c r="H52">
         <f>AVERAGE(H38:H42)</f>
-        <v>2892.6</v>
+        <v>2277</v>
       </c>
       <c r="I52">
         <f>AVERAGE(I38:I42)</f>
-        <v>2688.6</v>
+        <v>2279</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
@@ -11083,10 +11098,10 @@
         <v>14</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
@@ -11103,11 +11118,11 @@
       </c>
       <c r="J58" s="14">
         <f>(G49 - H49) / G49</f>
-        <v>-0.25738636363636369</v>
+        <v>-9.8011363636363633E-2</v>
       </c>
       <c r="K58" s="14">
         <f>(G49 - I49) / G49</f>
-        <v>-0.17073863636363643</v>
+        <v>-8.1250000000000058E-2</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
@@ -11124,11 +11139,11 @@
       </c>
       <c r="J59" s="14">
         <f t="shared" ref="J59:J61" si="6">(G50 - H50) / G50</f>
-        <v>-0.31076414952709802</v>
+        <v>5.5397087524395698E-2</v>
       </c>
       <c r="K59" s="14">
         <f t="shared" ref="K59:K61" si="7">(G50 - I50) / G50</f>
-        <v>6.0051043386878849E-3</v>
+        <v>6.0951809037682061E-2</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
@@ -11145,11 +11160,11 @@
       </c>
       <c r="J60" s="14">
         <f t="shared" si="6"/>
-        <v>-0.53861092072195582</v>
+        <v>6.636965958419011E-2</v>
       </c>
       <c r="K60" s="14">
         <f t="shared" si="7"/>
-        <v>-0.28775416952250399</v>
+        <v>9.5841900845327829E-2</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
@@ -11166,11 +11181,11 @@
       </c>
       <c r="J61" s="14">
         <f t="shared" si="6"/>
-        <v>-0.29899407221124469</v>
+        <v>-2.2543560265852261E-2</v>
       </c>
       <c r="K61" s="14">
         <f t="shared" si="7"/>
-        <v>-0.20738279144961366</v>
+        <v>-2.3441710077240802E-2</v>
       </c>
     </row>
   </sheetData>
@@ -11193,7 +11208,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24.28515625" bestFit="1" customWidth="1"/>
@@ -11207,1075 +11222,978 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="A1" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+    </row>
+    <row r="3" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" s="2"/>
+      <c r="B3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>2</v>
-      </c>
-      <c r="B2">
-        <v>15.933999999999999</v>
-      </c>
-      <c r="C2">
-        <v>18.88</v>
-      </c>
-      <c r="D2">
-        <v>1.571</v>
-      </c>
-      <c r="E2">
-        <v>5.0659999999999998</v>
-      </c>
-      <c r="F2">
-        <v>0.114</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
+      <c r="G3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>1.2490000000000001</v>
+      </c>
+      <c r="C4">
+        <v>1.173</v>
+      </c>
+      <c r="D4">
+        <v>0.44</v>
+      </c>
+      <c r="E4">
+        <v>0.254</v>
+      </c>
+      <c r="F4">
+        <v>0.49399999999999999</v>
+      </c>
+      <c r="G4">
+        <v>0.46200000000000002</v>
+      </c>
+      <c r="H4">
+        <v>0.61399999999999999</v>
+      </c>
+      <c r="I4">
+        <v>0.66400000000000003</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>1.355</v>
+      </c>
+      <c r="C5">
+        <v>1.32</v>
+      </c>
+      <c r="D5">
+        <v>0.49299999999999999</v>
+      </c>
+      <c r="E5">
+        <v>0.20799999999999999</v>
+      </c>
+      <c r="F5">
+        <v>0.502</v>
+      </c>
+      <c r="G5">
+        <v>0.45100000000000001</v>
+      </c>
+      <c r="H5">
+        <v>0.75800000000000001</v>
+      </c>
+      <c r="I5">
+        <v>0.629</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6">
+        <v>1.306</v>
+      </c>
+      <c r="C6">
+        <v>1.181</v>
+      </c>
+      <c r="D6">
+        <v>0.55900000000000005</v>
+      </c>
+      <c r="E6">
+        <v>0.22500000000000001</v>
+      </c>
+      <c r="F6">
+        <v>0.497</v>
+      </c>
+      <c r="G6">
+        <v>0.46899999999999997</v>
+      </c>
+      <c r="H6">
+        <v>0.627</v>
+      </c>
+      <c r="I6">
+        <v>0.68300000000000005</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>1.4650000000000001</v>
+      </c>
+      <c r="C7">
+        <v>1.171</v>
+      </c>
+      <c r="D7">
+        <v>0.53600000000000003</v>
+      </c>
+      <c r="E7">
+        <v>0.27900000000000003</v>
+      </c>
+      <c r="F7">
+        <v>0.59599999999999997</v>
+      </c>
+      <c r="G7">
+        <v>0.52400000000000002</v>
+      </c>
+      <c r="H7">
+        <v>0.65800000000000003</v>
+      </c>
+      <c r="I7">
+        <v>0.69799999999999995</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>1.375</v>
+      </c>
+      <c r="C8">
+        <v>1.4430000000000001</v>
+      </c>
+      <c r="D8">
+        <v>0.53300000000000003</v>
+      </c>
+      <c r="E8">
+        <v>0.20899999999999999</v>
+      </c>
+      <c r="F8">
+        <v>0.52400000000000002</v>
+      </c>
+      <c r="G8">
+        <v>0.434</v>
+      </c>
+      <c r="H8">
+        <v>0.50600000000000001</v>
+      </c>
+      <c r="I8">
+        <v>0.63800000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="15"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+    </row>
+    <row r="13" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A13" s="2"/>
+      <c r="B13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3">
-        <v>27.42</v>
-      </c>
-      <c r="C3">
-        <v>524</v>
-      </c>
-      <c r="D3">
-        <v>17.623999999999999</v>
-      </c>
-      <c r="E3">
-        <v>17.466999999999999</v>
-      </c>
-      <c r="F3">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>8</v>
-      </c>
-      <c r="B4">
-        <v>30.62</v>
-      </c>
-      <c r="C4">
-        <v>3632.2669999999998</v>
-      </c>
-      <c r="D4">
-        <v>1.5309999999999999</v>
-      </c>
-      <c r="E4">
-        <v>3603.252</v>
-      </c>
-      <c r="F4">
-        <v>0.34899999999999998</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>16</v>
-      </c>
-      <c r="B5">
-        <v>49.719000000000001</v>
-      </c>
-      <c r="C5">
-        <v>3649.7190000000001</v>
-      </c>
-      <c r="D5">
-        <v>11.948</v>
-      </c>
-      <c r="E5">
-        <v>3617.8020000000001</v>
-      </c>
-      <c r="F5">
-        <v>0.52100000000000002</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="16"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-    </row>
-    <row r="12" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A12" s="2"/>
-      <c r="B12" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G12" s="1" t="s">
+      <c r="G13" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H12" s="10" t="s">
+      <c r="H13" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="I12" s="11" t="s">
+      <c r="I13" s="11" t="s">
         <v>39</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13">
-        <v>1.2490000000000001</v>
-      </c>
-      <c r="C13">
-        <v>1.173</v>
-      </c>
-      <c r="D13">
-        <v>0.44</v>
-      </c>
-      <c r="E13">
-        <v>0.254</v>
-      </c>
-      <c r="F13">
-        <v>0.49399999999999999</v>
-      </c>
-      <c r="G13">
-        <v>0.46200000000000002</v>
-      </c>
-      <c r="H13">
-        <v>0.46</v>
-      </c>
-      <c r="I13">
-        <v>0.48399999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B14">
-        <v>1.355</v>
+        <v>2.4489999999999998</v>
       </c>
       <c r="C14">
-        <v>1.32</v>
+        <v>2.1520000000000001</v>
       </c>
       <c r="D14">
-        <v>0.49299999999999999</v>
+        <v>0.433</v>
       </c>
       <c r="E14">
-        <v>0.20799999999999999</v>
+        <v>0.23300000000000001</v>
       </c>
       <c r="F14">
-        <v>0.502</v>
+        <v>0.59</v>
       </c>
       <c r="G14">
-        <v>0.45100000000000001</v>
+        <v>0.71499999999999997</v>
       </c>
       <c r="H14">
-        <v>0.50900000000000001</v>
+        <v>0.77500000000000002</v>
       </c>
       <c r="I14">
-        <v>0.42299999999999999</v>
+        <v>0.83799999999999997</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B15">
-        <v>1.306</v>
+        <v>2.62</v>
       </c>
       <c r="C15">
-        <v>1.181</v>
+        <v>2.4990000000000001</v>
       </c>
       <c r="D15">
-        <v>0.55900000000000005</v>
+        <v>0.46500000000000002</v>
       </c>
       <c r="E15">
-        <v>0.22500000000000001</v>
+        <v>0.33100000000000002</v>
       </c>
       <c r="F15">
-        <v>0.497</v>
+        <v>0.66700000000000004</v>
       </c>
       <c r="G15">
-        <v>0.46899999999999997</v>
+        <v>0.76100000000000001</v>
       </c>
       <c r="H15">
-        <v>0.627</v>
+        <v>0.92600000000000005</v>
       </c>
       <c r="I15">
-        <v>0.47199999999999998</v>
+        <v>0.82399999999999995</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B16">
-        <v>1.4650000000000001</v>
+        <v>2.2519999999999998</v>
       </c>
       <c r="C16">
-        <v>1.171</v>
+        <v>2.1709999999999998</v>
       </c>
       <c r="D16">
-        <v>0.53600000000000003</v>
+        <v>0.443</v>
       </c>
       <c r="E16">
-        <v>0.27900000000000003</v>
+        <v>0.24199999999999999</v>
       </c>
       <c r="F16">
-        <v>0.59599999999999997</v>
+        <v>0.71799999999999997</v>
       </c>
       <c r="G16">
-        <v>0.52400000000000002</v>
+        <v>0.749</v>
       </c>
       <c r="H16">
-        <v>0.65800000000000003</v>
+        <v>0.85599999999999998</v>
       </c>
       <c r="I16">
-        <v>0.46700000000000003</v>
+        <v>0.63900000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17">
+        <v>2.2050000000000001</v>
+      </c>
+      <c r="C17">
+        <v>2.0910000000000002</v>
+      </c>
+      <c r="D17">
+        <v>0.45400000000000001</v>
+      </c>
+      <c r="E17">
+        <v>0.246</v>
+      </c>
+      <c r="F17">
+        <v>0.628</v>
+      </c>
+      <c r="G17">
+        <v>0.875</v>
+      </c>
+      <c r="H17">
+        <v>0.86899999999999999</v>
+      </c>
+      <c r="I17">
+        <v>0.94499999999999995</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B17">
-        <v>1.375</v>
-      </c>
-      <c r="C17">
-        <v>1.4430000000000001</v>
-      </c>
-      <c r="D17">
-        <v>0.53300000000000003</v>
-      </c>
-      <c r="E17">
-        <v>0.20899999999999999</v>
-      </c>
-      <c r="F17">
-        <v>0.52400000000000002</v>
-      </c>
-      <c r="G17">
-        <v>0.434</v>
-      </c>
-      <c r="H17">
-        <v>0.50600000000000001</v>
-      </c>
-      <c r="I17">
-        <v>0.47299999999999998</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
+      <c r="B18">
+        <v>2.1520000000000001</v>
+      </c>
+      <c r="C18">
+        <v>2.2610000000000001</v>
+      </c>
+      <c r="D18">
+        <v>0.443</v>
+      </c>
+      <c r="E18">
+        <v>0.23400000000000001</v>
+      </c>
+      <c r="F18">
+        <v>0.59499999999999997</v>
+      </c>
+      <c r="G18">
+        <v>0.94599999999999995</v>
+      </c>
+      <c r="H18">
+        <v>0.83299999999999996</v>
+      </c>
+      <c r="I18">
+        <v>0.88200000000000001</v>
+      </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="16" t="s">
+      <c r="A21" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
-    </row>
-    <row r="22" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A22" s="2"/>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
+    </row>
+    <row r="23" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A23" s="2"/>
+      <c r="B23" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C23" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D23" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="E23" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="F23" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="G23" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H22" s="10" t="s">
+      <c r="H23" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="I22" s="11" t="s">
+      <c r="I23" s="11" t="s">
         <v>39</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B23">
-        <v>2.4489999999999998</v>
-      </c>
-      <c r="C23">
-        <v>2.1520000000000001</v>
-      </c>
-      <c r="D23">
-        <v>0.433</v>
-      </c>
-      <c r="E23">
-        <v>0.23300000000000001</v>
-      </c>
-      <c r="F23">
-        <v>0.59</v>
-      </c>
-      <c r="G23">
-        <v>0.71499999999999997</v>
-      </c>
-      <c r="H23">
-        <v>1.0329999999999999</v>
-      </c>
-      <c r="I23">
-        <v>0.89</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B24">
-        <v>2.62</v>
+        <v>4.0389999999999997</v>
       </c>
       <c r="C24">
-        <v>2.4990000000000001</v>
+        <v>3.92</v>
       </c>
       <c r="D24">
-        <v>0.46500000000000002</v>
+        <v>0.57499999999999996</v>
       </c>
       <c r="E24">
-        <v>0.33100000000000002</v>
+        <v>0.25900000000000001</v>
       </c>
       <c r="F24">
-        <v>0.66700000000000004</v>
+        <v>0.70099999999999996</v>
       </c>
       <c r="G24">
-        <v>0.76100000000000001</v>
+        <v>1.387</v>
       </c>
       <c r="H24">
-        <v>0.90100000000000002</v>
+        <v>0.95299999999999996</v>
       </c>
       <c r="I24">
-        <v>0.82399999999999995</v>
+        <v>1.0489999999999999</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B25">
-        <v>2.2519999999999998</v>
+        <v>3.802</v>
       </c>
       <c r="C25">
-        <v>2.1709999999999998</v>
+        <v>3.7509999999999999</v>
       </c>
       <c r="D25">
-        <v>0.443</v>
+        <v>0.51600000000000001</v>
       </c>
       <c r="E25">
-        <v>0.24199999999999999</v>
+        <v>0.29199999999999998</v>
       </c>
       <c r="F25">
-        <v>0.71799999999999997</v>
+        <v>0.69099999999999995</v>
       </c>
       <c r="G25">
-        <v>0.749</v>
+        <v>0.82599999999999996</v>
       </c>
       <c r="H25">
-        <v>0.85599999999999998</v>
+        <v>1.087</v>
       </c>
       <c r="I25">
-        <v>0.63900000000000001</v>
+        <v>1.2170000000000001</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B26">
-        <v>2.2050000000000001</v>
+        <v>3.8849999999999998</v>
       </c>
       <c r="C26">
-        <v>2.0910000000000002</v>
+        <v>3.794</v>
       </c>
       <c r="D26">
-        <v>0.45400000000000001</v>
+        <v>0.45700000000000002</v>
       </c>
       <c r="E26">
-        <v>0.246</v>
+        <v>0.28499999999999998</v>
       </c>
       <c r="F26">
-        <v>0.628</v>
+        <v>0.97099999999999997</v>
       </c>
       <c r="G26">
-        <v>0.875</v>
+        <v>1.03</v>
       </c>
       <c r="H26">
-        <v>0.86899999999999999</v>
+        <v>1.133</v>
       </c>
       <c r="I26">
-        <v>0.94499999999999995</v>
+        <v>0.90300000000000002</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27">
+        <v>3.7490000000000001</v>
+      </c>
+      <c r="C27">
+        <v>3.7869999999999999</v>
+      </c>
+      <c r="D27">
+        <v>0.55100000000000005</v>
+      </c>
+      <c r="E27">
+        <v>0.31</v>
+      </c>
+      <c r="F27">
+        <v>0.77400000000000002</v>
+      </c>
+      <c r="G27">
+        <v>0.94299999999999995</v>
+      </c>
+      <c r="H27">
+        <v>1.131</v>
+      </c>
+      <c r="I27">
+        <v>1.2809999999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B27">
-        <v>2.1520000000000001</v>
-      </c>
-      <c r="C27">
-        <v>2.2610000000000001</v>
-      </c>
-      <c r="D27">
-        <v>0.443</v>
-      </c>
-      <c r="E27">
-        <v>0.23400000000000001</v>
-      </c>
-      <c r="F27">
-        <v>0.59499999999999997</v>
-      </c>
-      <c r="G27">
-        <v>0.94599999999999995</v>
-      </c>
-      <c r="H27">
-        <v>0.83299999999999996</v>
-      </c>
-      <c r="I27">
-        <v>1.1120000000000001</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30" s="15"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="16" t="s">
+      <c r="B28">
+        <v>4.0529999999999999</v>
+      </c>
+      <c r="C28">
+        <v>4.2370000000000001</v>
+      </c>
+      <c r="D28">
+        <v>0.48399999999999999</v>
+      </c>
+      <c r="E28">
+        <v>0.32100000000000001</v>
+      </c>
+      <c r="F28">
+        <v>0.68</v>
+      </c>
+      <c r="G28">
+        <v>0.996</v>
+      </c>
+      <c r="H28">
+        <v>1.147</v>
+      </c>
+      <c r="I28">
+        <v>1.363</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32" s="15"/>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="15"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="B31" s="16"/>
-      <c r="C31" s="16"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="16"/>
-    </row>
-    <row r="32" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A32" s="2"/>
-      <c r="B32" s="1" t="s">
+      <c r="B33" s="16"/>
+      <c r="C33" s="16"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="16"/>
+    </row>
+    <row r="34" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A34" s="2"/>
+      <c r="B34" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C34" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D34" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E32" s="3" t="s">
+      <c r="E34" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="F34" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G32" s="1" t="s">
+      <c r="G34" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H32" s="10" t="s">
+      <c r="H34" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="I32" s="11" t="s">
+      <c r="I34" s="11" t="s">
         <v>39</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B33">
-        <v>4.0389999999999997</v>
-      </c>
-      <c r="C33">
-        <v>3.92</v>
-      </c>
-      <c r="D33">
-        <v>0.57499999999999996</v>
-      </c>
-      <c r="E33">
-        <v>0.25900000000000001</v>
-      </c>
-      <c r="F33">
-        <v>0.70099999999999996</v>
-      </c>
-      <c r="G33">
-        <v>1.387</v>
-      </c>
-      <c r="H33">
-        <v>1.2070000000000001</v>
-      </c>
-      <c r="I33">
-        <v>1.0489999999999999</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B34">
-        <v>3.802</v>
-      </c>
-      <c r="C34">
-        <v>3.7509999999999999</v>
-      </c>
-      <c r="D34">
-        <v>0.51600000000000001</v>
-      </c>
-      <c r="E34">
-        <v>0.29199999999999998</v>
-      </c>
-      <c r="F34">
-        <v>0.69099999999999995</v>
-      </c>
-      <c r="G34">
-        <v>0.82599999999999996</v>
-      </c>
-      <c r="H34">
-        <v>1.139</v>
-      </c>
-      <c r="I34">
-        <v>1.071</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B35">
-        <v>3.8849999999999998</v>
+        <v>4.1980000000000004</v>
       </c>
       <c r="C35">
-        <v>3.794</v>
+        <v>4.0369999999999999</v>
       </c>
       <c r="D35">
-        <v>0.45700000000000002</v>
+        <v>0.96699999999999997</v>
       </c>
       <c r="E35">
-        <v>0.28499999999999998</v>
+        <v>0.41599999999999998</v>
       </c>
       <c r="F35">
-        <v>0.97099999999999997</v>
+        <v>0.98399999999999999</v>
       </c>
       <c r="G35">
-        <v>1.03</v>
+        <v>1.1160000000000001</v>
       </c>
       <c r="H35">
-        <v>1.653</v>
+        <v>1.0309999999999999</v>
       </c>
       <c r="I35">
-        <v>0.90300000000000002</v>
+        <v>1.353</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B36">
-        <v>3.7490000000000001</v>
+        <v>4.0410000000000004</v>
       </c>
       <c r="C36">
-        <v>3.7869999999999999</v>
+        <v>3.8130000000000002</v>
       </c>
       <c r="D36">
-        <v>0.55100000000000005</v>
+        <v>1.0660000000000001</v>
       </c>
       <c r="E36">
-        <v>0.31</v>
+        <v>0.58899999999999997</v>
       </c>
       <c r="F36">
-        <v>0.77400000000000002</v>
+        <v>0.77200000000000002</v>
       </c>
       <c r="G36">
-        <v>0.94299999999999995</v>
+        <v>1.248</v>
       </c>
       <c r="H36">
-        <v>1.3640000000000001</v>
+        <v>1.254</v>
       </c>
       <c r="I36">
-        <v>1.2809999999999999</v>
+        <v>1.266</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B37">
+        <v>3.68</v>
+      </c>
+      <c r="C37">
+        <v>3.9620000000000002</v>
+      </c>
+      <c r="D37">
+        <v>1.002</v>
+      </c>
+      <c r="E37">
+        <v>0.52600000000000002</v>
+      </c>
+      <c r="F37">
+        <v>1.3839999999999999</v>
+      </c>
+      <c r="G37">
+        <v>1.7330000000000001</v>
+      </c>
+      <c r="H37">
+        <v>1.4410000000000001</v>
+      </c>
+      <c r="I37">
+        <v>1.288</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B38">
+        <v>4.141</v>
+      </c>
+      <c r="C38">
+        <v>3.8340000000000001</v>
+      </c>
+      <c r="D38">
+        <v>0.89700000000000002</v>
+      </c>
+      <c r="E38">
+        <v>0.48799999999999999</v>
+      </c>
+      <c r="F38">
+        <v>1.1140000000000001</v>
+      </c>
+      <c r="G38">
+        <v>1.64</v>
+      </c>
+      <c r="H38">
+        <v>1.351</v>
+      </c>
+      <c r="I38">
+        <v>1.268</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B37">
-        <v>4.0529999999999999</v>
-      </c>
-      <c r="C37">
-        <v>4.2370000000000001</v>
-      </c>
-      <c r="D37">
-        <v>0.48399999999999999</v>
-      </c>
-      <c r="E37">
-        <v>0.32100000000000001</v>
-      </c>
-      <c r="F37">
-        <v>0.68</v>
-      </c>
-      <c r="G37">
-        <v>0.996</v>
-      </c>
-      <c r="H37">
-        <v>1.6479999999999999</v>
-      </c>
-      <c r="I37">
-        <v>1.363</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="B41" s="15"/>
-      <c r="C41" s="15"/>
-      <c r="D41" s="15"/>
-      <c r="E41" s="15"/>
-      <c r="F41" s="15"/>
-      <c r="G41" s="15"/>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="B42" s="16"/>
-      <c r="C42" s="16"/>
-      <c r="D42" s="16"/>
-      <c r="E42" s="16"/>
-      <c r="F42" s="16"/>
-      <c r="G42" s="16"/>
-    </row>
-    <row r="43" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A43" s="2"/>
-      <c r="B43" s="1" t="s">
+      <c r="B39">
+        <v>4.1619999999999999</v>
+      </c>
+      <c r="C39">
+        <v>3.8439999999999999</v>
+      </c>
+      <c r="D39">
+        <v>0.91800000000000004</v>
+      </c>
+      <c r="E39">
+        <v>0.46100000000000002</v>
+      </c>
+      <c r="F39">
+        <v>1.373</v>
+      </c>
+      <c r="G39">
+        <v>1.8759999999999999</v>
+      </c>
+      <c r="H39">
+        <v>1.3240000000000001</v>
+      </c>
+      <c r="I39">
+        <v>1.3620000000000001</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B53" s="17"/>
+      <c r="C53" s="17"/>
+      <c r="D53" s="17"/>
+      <c r="E53" s="17"/>
+      <c r="F53" s="17"/>
+      <c r="G53" s="17"/>
+    </row>
+    <row r="54" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A54" s="2"/>
+      <c r="B54" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="C54" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="D54" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E43" s="3" t="s">
+      <c r="E54" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F43" s="1" t="s">
+      <c r="F54" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G43" s="1" t="s">
+      <c r="G54" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H43" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="I43" s="11" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B44">
-        <v>4.1980000000000004</v>
-      </c>
-      <c r="C44">
-        <v>4.0369999999999999</v>
-      </c>
-      <c r="D44">
-        <v>0.96699999999999997</v>
-      </c>
-      <c r="E44">
-        <v>0.41599999999999998</v>
-      </c>
-      <c r="F44">
-        <v>0.98399999999999999</v>
-      </c>
-      <c r="G44">
-        <v>1.1160000000000001</v>
-      </c>
-      <c r="H44">
-        <v>1.0309999999999999</v>
-      </c>
-      <c r="I44">
-        <v>1.706</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B45">
-        <v>4.0410000000000004</v>
-      </c>
-      <c r="C45">
-        <v>3.8130000000000002</v>
-      </c>
-      <c r="D45">
-        <v>1.0660000000000001</v>
-      </c>
-      <c r="E45">
-        <v>0.58899999999999997</v>
-      </c>
-      <c r="F45">
-        <v>0.77200000000000002</v>
-      </c>
-      <c r="G45">
-        <v>1.248</v>
-      </c>
-      <c r="H45">
-        <v>1.254</v>
-      </c>
-      <c r="I45">
-        <v>1.9610000000000001</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B46">
-        <v>3.68</v>
-      </c>
-      <c r="C46">
-        <v>3.9620000000000002</v>
-      </c>
-      <c r="D46">
-        <v>1.002</v>
-      </c>
-      <c r="E46">
-        <v>0.52600000000000002</v>
-      </c>
-      <c r="F46">
-        <v>1.3839999999999999</v>
-      </c>
-      <c r="G46">
-        <v>1.7330000000000001</v>
-      </c>
-      <c r="H46">
-        <v>1.4410000000000001</v>
-      </c>
-      <c r="I46">
-        <v>1.4359999999999999</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B47">
-        <v>4.141</v>
-      </c>
-      <c r="C47">
-        <v>3.8340000000000001</v>
-      </c>
-      <c r="D47">
-        <v>0.89700000000000002</v>
-      </c>
-      <c r="E47">
-        <v>0.48799999999999999</v>
-      </c>
-      <c r="F47">
-        <v>1.1140000000000001</v>
-      </c>
-      <c r="G47">
-        <v>1.64</v>
-      </c>
-      <c r="H47">
-        <v>1.7290000000000001</v>
-      </c>
-      <c r="I47">
-        <v>1.268</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B48">
-        <v>4.1619999999999999</v>
-      </c>
-      <c r="C48">
-        <v>3.8439999999999999</v>
-      </c>
-      <c r="D48">
-        <v>0.91800000000000004</v>
-      </c>
-      <c r="E48">
-        <v>0.46100000000000002</v>
-      </c>
-      <c r="F48">
-        <v>1.373</v>
-      </c>
-      <c r="G48">
-        <v>1.8759999999999999</v>
-      </c>
-      <c r="H48">
-        <v>1.4510000000000001</v>
-      </c>
-      <c r="I48">
-        <v>1.3620000000000001</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A62" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="B62" s="17"/>
-      <c r="C62" s="17"/>
-      <c r="D62" s="17"/>
-      <c r="E62" s="17"/>
-      <c r="F62" s="17"/>
-      <c r="G62" s="17"/>
-    </row>
-    <row r="63" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A63" s="2"/>
-      <c r="B63" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E63" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F63" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G63" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H63" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="I63" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A64" s="1">
+      <c r="H54" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
         <v>2</v>
       </c>
-      <c r="B64">
-        <f t="shared" ref="B64:G64" si="0">AVERAGE(B13:B17)</f>
+      <c r="B55">
+        <f t="shared" ref="B55:G55" si="0">AVERAGE(B4:B8)</f>
         <v>1.35</v>
       </c>
-      <c r="C64">
+      <c r="C55">
         <f t="shared" si="0"/>
         <v>1.2576000000000001</v>
       </c>
-      <c r="D64">
+      <c r="D55">
         <f t="shared" si="0"/>
         <v>0.51219999999999999</v>
       </c>
-      <c r="E64">
+      <c r="E55">
         <f t="shared" si="0"/>
         <v>0.23500000000000001</v>
       </c>
-      <c r="F64">
+      <c r="F55">
         <f t="shared" si="0"/>
         <v>0.52259999999999995</v>
       </c>
-      <c r="G64">
+      <c r="G55">
         <f t="shared" si="0"/>
         <v>0.46800000000000008</v>
       </c>
-      <c r="H64">
-        <f>AVERAGE(H13:H17)</f>
-        <v>0.55199999999999994</v>
-      </c>
-      <c r="I64">
-        <f>AVERAGE(I13:I17)</f>
-        <v>0.46379999999999999</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A65" s="1">
+      <c r="H55">
+        <f>AVERAGE(H4:H8)</f>
+        <v>0.63260000000000005</v>
+      </c>
+      <c r="I55">
+        <f>AVERAGE(I4:I8)</f>
+        <v>0.6624000000000001</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
         <v>4</v>
       </c>
-      <c r="B65">
-        <f t="shared" ref="B65:G65" si="1">AVERAGE(B23:B27)</f>
+      <c r="B56">
+        <f t="shared" ref="B56:G56" si="1">AVERAGE(B14:B18)</f>
         <v>2.3356000000000003</v>
       </c>
-      <c r="C65">
+      <c r="C56">
         <f t="shared" si="1"/>
         <v>2.2347999999999999</v>
       </c>
-      <c r="D65">
+      <c r="D56">
         <f t="shared" si="1"/>
         <v>0.4476</v>
       </c>
-      <c r="E65">
+      <c r="E56">
         <f t="shared" si="1"/>
         <v>0.25719999999999998</v>
       </c>
-      <c r="F65">
+      <c r="F56">
         <f t="shared" si="1"/>
         <v>0.63960000000000006</v>
       </c>
-      <c r="G65">
+      <c r="G56">
         <f t="shared" si="1"/>
         <v>0.80920000000000003</v>
       </c>
-      <c r="H65">
-        <f>AVERAGE(H23:H27)</f>
-        <v>0.89839999999999998</v>
-      </c>
-      <c r="I65">
-        <f>AVERAGE(I23:I27)</f>
-        <v>0.88200000000000001</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A66" s="1">
+      <c r="H56">
+        <f>AVERAGE(H14:H18)</f>
+        <v>0.85180000000000011</v>
+      </c>
+      <c r="I56">
+        <f>AVERAGE(I14:I18)</f>
+        <v>0.8256</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
         <v>8</v>
       </c>
-      <c r="B66">
-        <f t="shared" ref="B66:G66" si="2">AVERAGE(B33:B37)</f>
+      <c r="B57">
+        <f t="shared" ref="B57:G57" si="2">AVERAGE(B24:B28)</f>
         <v>3.9055999999999997</v>
       </c>
-      <c r="C66">
+      <c r="C57">
         <f t="shared" si="2"/>
         <v>3.8977999999999993</v>
       </c>
-      <c r="D66">
+      <c r="D57">
         <f t="shared" si="2"/>
         <v>0.51660000000000006</v>
       </c>
-      <c r="E66">
+      <c r="E57">
         <f t="shared" si="2"/>
         <v>0.29339999999999999</v>
       </c>
-      <c r="F66">
+      <c r="F57">
         <f t="shared" si="2"/>
         <v>0.76340000000000008</v>
       </c>
-      <c r="G66">
+      <c r="G57">
         <f t="shared" si="2"/>
         <v>1.0364</v>
       </c>
-      <c r="H66">
-        <f>AVERAGE(H33:H37)</f>
-        <v>1.4022000000000001</v>
-      </c>
-      <c r="I66">
-        <f>AVERAGE(I33:I37)</f>
-        <v>1.1334</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A67" s="1">
+      <c r="H57">
+        <f>AVERAGE(H24:H28)</f>
+        <v>1.0902000000000001</v>
+      </c>
+      <c r="I57">
+        <f>AVERAGE(I24:I28)</f>
+        <v>1.1626000000000001</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
         <v>16</v>
       </c>
-      <c r="B67">
-        <f t="shared" ref="B67:G67" si="3">AVERAGE(B44:B48)</f>
+      <c r="B58">
+        <f t="shared" ref="B58:G58" si="3">AVERAGE(B35:B39)</f>
         <v>4.0444000000000004</v>
       </c>
-      <c r="C67">
+      <c r="C58">
         <f t="shared" si="3"/>
         <v>3.8979999999999997</v>
       </c>
-      <c r="D67">
+      <c r="D58">
         <f t="shared" si="3"/>
         <v>0.97000000000000008</v>
       </c>
-      <c r="E67">
+      <c r="E58">
         <f t="shared" si="3"/>
         <v>0.496</v>
       </c>
-      <c r="F67">
+      <c r="F58">
         <f t="shared" si="3"/>
         <v>1.1254</v>
       </c>
-      <c r="G67">
+      <c r="G58">
         <f t="shared" si="3"/>
         <v>1.5226</v>
       </c>
-      <c r="H67">
-        <f>AVERAGE(H44:H48)</f>
-        <v>1.3812000000000002</v>
-      </c>
-      <c r="I67">
-        <f>AVERAGE(I44:I48)</f>
-        <v>1.5466</v>
+      <c r="H58">
+        <f>AVERAGE(H35:H39)</f>
+        <v>1.2802</v>
+      </c>
+      <c r="I58">
+        <f>AVERAGE(I35:I39)</f>
+        <v>1.3073999999999999</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A62:G62"/>
-    <mergeCell ref="A42:G42"/>
-    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A53:G53"/>
+    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
     <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A12:G12"/>
     <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A32:G32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -12393,7 +12311,7 @@
         <v>38</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
@@ -12440,7 +12358,7 @@
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>5.3E-3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -12484,7 +12402,7 @@
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>1.4E-2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -12510,7 +12428,7 @@
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>1.235E-2</v>
+        <v>0.100617</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -12536,7 +12454,7 @@
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>1.0500000000000001E-2</v>
+        <v>0.100617</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -12734,7 +12652,7 @@
         <v>0</v>
       </c>
       <c r="M21" s="13">
-        <v>1.0800000000000001E-2</v>
+        <v>0.10242999999999999</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
@@ -12756,7 +12674,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="13">
-        <v>1.44E-2</v>
+        <v>0.10242999999999999</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
@@ -12779,7 +12697,7 @@
         <v>0</v>
       </c>
       <c r="M23" s="13">
-        <v>1.26E-2</v>
+        <v>0.10242999999999999</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
@@ -12805,7 +12723,7 @@
         <v>0</v>
       </c>
       <c r="M24" s="13">
-        <v>1.089E-2</v>
+        <v>0.10242999999999999</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
@@ -12831,7 +12749,7 @@
         <v>0</v>
       </c>
       <c r="M25" s="13">
-        <v>1.078E-2</v>
+        <v>0.10242999999999999</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
@@ -13058,7 +12976,7 @@
         <v>0</v>
       </c>
       <c r="Q36">
-        <v>1.7600000000000001E-2</v>
+        <v>5.5599999999999997E-2</v>
       </c>
     </row>
     <row r="38" spans="9:17" x14ac:dyDescent="0.25">
@@ -13165,7 +13083,7 @@
         <v>0</v>
       </c>
       <c r="M44" s="13">
-        <v>1.6049999999999998E-2</v>
+        <v>5.5300000000000002E-2</v>
       </c>
     </row>
     <row r="47" spans="9:17" x14ac:dyDescent="0.25">
@@ -13404,7 +13322,7 @@
         <v>0</v>
       </c>
       <c r="N58" s="5">
-        <v>3.1780000000000003E-2</v>
+        <v>6.8699999999999997E-2</v>
       </c>
     </row>
     <row r="59" spans="9:17" x14ac:dyDescent="0.25">
@@ -13424,7 +13342,7 @@
         <v>0</v>
       </c>
       <c r="N59" s="5">
-        <v>2.9169999999999998E-2</v>
+        <v>5.5399999999999998E-2</v>
       </c>
     </row>
     <row r="60" spans="9:17" x14ac:dyDescent="0.25">
@@ -13444,7 +13362,7 @@
         <v>0</v>
       </c>
       <c r="N60" s="5">
-        <v>2.3719999999999998E-2</v>
+        <v>5.8900000000000001E-2</v>
       </c>
     </row>
     <row r="61" spans="9:17" x14ac:dyDescent="0.25">
@@ -13464,7 +13382,7 @@
         <v>0</v>
       </c>
       <c r="N61" s="5">
-        <v>3.3270000000000001E-2</v>
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="62" spans="9:17" x14ac:dyDescent="0.25">
@@ -13484,7 +13402,7 @@
         <v>0</v>
       </c>
       <c r="N62" s="5">
-        <v>2.775E-2</v>
+        <v>5.7000000000000002E-2</v>
       </c>
     </row>
     <row r="66" spans="9:17" x14ac:dyDescent="0.25">
@@ -13857,11 +13775,11 @@
       <c r="L88" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M88" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="N88" s="11" t="s">
-        <v>42</v>
+      <c r="M88" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="N88" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="89" spans="9:15" x14ac:dyDescent="0.25">
@@ -13885,7 +13803,7 @@
       </c>
       <c r="N89" s="14">
         <f>AVERAGE(Q4:Q8)</f>
-        <v>2.9430000000000001E-2</v>
+        <v>0.10124680000000001</v>
       </c>
     </row>
     <row r="90" spans="9:15" x14ac:dyDescent="0.25">
@@ -13909,7 +13827,7 @@
       </c>
       <c r="N90" s="14">
         <f>AVERAGE(Q32:Q36)</f>
-        <v>8.7414000000000006E-2</v>
+        <v>9.5014000000000001E-2</v>
       </c>
     </row>
     <row r="91" spans="9:15" x14ac:dyDescent="0.25">
@@ -14006,7 +13924,7 @@
       </c>
       <c r="N97" s="12">
         <f>AVERAGE(M21:M25)</f>
-        <v>1.1893999999999998E-2</v>
+        <v>0.10242999999999999</v>
       </c>
     </row>
     <row r="98" spans="9:14" x14ac:dyDescent="0.25">
@@ -14029,7 +13947,7 @@
       </c>
       <c r="N98" s="12">
         <f>AVERAGE(M40:M44)</f>
-        <v>3.2960000000000003E-2</v>
+        <v>4.0809999999999999E-2</v>
       </c>
     </row>
     <row r="99" spans="9:14" x14ac:dyDescent="0.25">
@@ -14053,7 +13971,7 @@
       </c>
       <c r="N99" s="5">
         <f>AVERAGE(N58:N62)</f>
-        <v>2.9137999999999997E-2</v>
+        <v>6.0999999999999999E-2</v>
       </c>
     </row>
     <row r="100" spans="9:14" x14ac:dyDescent="0.25">
@@ -14127,7 +14045,7 @@
   <sheetData>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="B2" s="24"/>
       <c r="C2" s="24"/>
@@ -14170,8 +14088,8 @@
       <c r="H4" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="I4" s="11" t="s">
-        <v>39</v>
+      <c r="I4" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -14255,7 +14173,7 @@
         <v>2</v>
       </c>
       <c r="H7" s="6">
-        <v>118</v>
+        <v>13</v>
       </c>
       <c r="I7" s="6">
         <v>9</v>
@@ -14391,7 +14309,7 @@
         <v>6</v>
       </c>
       <c r="H15">
-        <v>152</v>
+        <v>58</v>
       </c>
       <c r="I15">
         <v>39</v>
@@ -14420,7 +14338,7 @@
         <v>7</v>
       </c>
       <c r="H16">
-        <v>160</v>
+        <v>110</v>
       </c>
       <c r="I16">
         <v>63</v>
@@ -14449,7 +14367,7 @@
         <v>7</v>
       </c>
       <c r="H17">
-        <v>187</v>
+        <v>101</v>
       </c>
       <c r="I17">
         <v>19</v>
@@ -14478,7 +14396,7 @@
         <v>30</v>
       </c>
       <c r="H18">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="I18">
         <v>61</v>
@@ -14507,7 +14425,7 @@
         <v>9</v>
       </c>
       <c r="H19">
-        <v>168</v>
+        <v>63</v>
       </c>
       <c r="I19">
         <v>22</v>
@@ -14585,7 +14503,7 @@
         <v>11</v>
       </c>
       <c r="H29">
-        <v>292</v>
+        <v>124</v>
       </c>
       <c r="I29">
         <v>113</v>
@@ -14614,7 +14532,7 @@
         <v>18</v>
       </c>
       <c r="H30">
-        <v>235</v>
+        <v>104</v>
       </c>
       <c r="I30">
         <v>122</v>
@@ -14643,7 +14561,7 @@
         <v>18</v>
       </c>
       <c r="H31">
-        <v>406</v>
+        <v>92</v>
       </c>
       <c r="I31">
         <v>132</v>
@@ -14672,7 +14590,7 @@
         <v>14</v>
       </c>
       <c r="H32">
-        <v>346</v>
+        <v>114</v>
       </c>
       <c r="I32">
         <v>116</v>
@@ -14701,7 +14619,7 @@
         <v>19</v>
       </c>
       <c r="H33">
-        <v>367</v>
+        <v>101</v>
       </c>
       <c r="I33">
         <v>112</v>
@@ -14779,10 +14697,10 @@
         <v>77</v>
       </c>
       <c r="H41">
-        <v>285</v>
+        <v>132</v>
       </c>
       <c r="I41">
-        <v>201</v>
+        <v>195</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -14808,10 +14726,10 @@
         <v>65</v>
       </c>
       <c r="H42">
-        <v>255</v>
+        <v>197</v>
       </c>
       <c r="I42">
-        <v>323</v>
+        <v>183</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
@@ -14837,10 +14755,10 @@
         <v>64</v>
       </c>
       <c r="H43">
-        <v>369</v>
+        <v>179</v>
       </c>
       <c r="I43">
-        <v>277</v>
+        <v>161</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
@@ -14866,10 +14784,10 @@
         <v>93</v>
       </c>
       <c r="H44">
-        <v>341</v>
+        <v>242</v>
       </c>
       <c r="I44">
-        <v>201</v>
+        <v>180</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
@@ -14895,10 +14813,10 @@
         <v>95</v>
       </c>
       <c r="H45">
-        <v>417</v>
+        <v>192</v>
       </c>
       <c r="I45">
-        <v>238</v>
+        <v>183</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
@@ -14969,7 +14887,7 @@
       </c>
       <c r="H51">
         <f>AVERAGE(H5:H9)</f>
-        <v>40.6</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="I51">
         <f>AVERAGE(I5:I9)</f>
@@ -15006,7 +14924,7 @@
       </c>
       <c r="H52">
         <f>AVERAGE(H15:H19)</f>
-        <v>164.4</v>
+        <v>84</v>
       </c>
       <c r="I52">
         <f>AVERAGE(I15:I19)</f>
@@ -15043,7 +14961,7 @@
       </c>
       <c r="H53">
         <f>AVERAGE(H29:H33)</f>
-        <v>329.2</v>
+        <v>107</v>
       </c>
       <c r="I53">
         <f>AVERAGE(I29:I33)</f>
@@ -15080,11 +14998,11 @@
       </c>
       <c r="H54">
         <f>AVERAGE(H41:H45)</f>
-        <v>333.4</v>
+        <v>188.4</v>
       </c>
       <c r="I54">
         <f>AVERAGE(I41:I45)</f>
-        <v>248</v>
+        <v>180.4</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.25">

--- a/Experiments data/K Size/K_Size_Email_Graph.xlsx
+++ b/Experiments data/K Size/K_Size_Email_Graph.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fengw\OneDrive\Documents\GitHub\KaMinPar_Java\Experiments data\K Size\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C114C28C-25A1-45BE-9D63-95858797BEA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B25071AC-EC10-41D6-8371-9B2555EAE6CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-210" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Edge Cuts" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="51">
   <si>
     <t>Proposed w/PRRP w/o ILP</t>
   </si>
@@ -186,6 +186,9 @@
   </si>
   <si>
     <t>Deep NUGP, ε= 0.0</t>
+  </si>
+  <si>
+    <t>Deep NUGP, ε relaxed</t>
   </si>
 </sst>
 </file>
@@ -366,14 +369,14 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1842,7 +1845,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep NUGP, ε = 57</c:v>
+                  <c:v>Deep NUGP, ε relaxed</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2034,12 +2037,27 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1800"/>
-                  <a:t>% of Improvment</a:t>
+                  <a:rPr lang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Precentage of Improvment</a:t>
                 </a:r>
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="2.0555093462406176E-2"/>
+              <c:y val="0.26179281249571956"/>
+            </c:manualLayout>
+          </c:layout>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -2552,7 +2570,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep NUGP, ε = 57</c:v>
+                  <c:v>Deep NUGP, ε relaxed</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4605,7 +4623,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep NUGP, ε = 57</c:v>
+                  <c:v>Deep NUGP, ε relaxed</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -11101,7 +11119,7 @@
         <v>49</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
@@ -12032,7 +12050,7 @@
         <v>49</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
@@ -12484,11 +12502,11 @@
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="I11" s="19" t="s">
+      <c r="I11" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="J11" s="19"/>
-      <c r="K11" s="19"/>
+      <c r="J11" s="20"/>
+      <c r="K11" s="20"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="J12" s="1" t="s">
@@ -12499,16 +12517,16 @@
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19" t="s">
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
       <c r="I13" s="1" t="s">
         <v>5</v>
       </c>
@@ -12617,11 +12635,11 @@
       <c r="C19" s="4">
         <v>1</v>
       </c>
-      <c r="I19" s="18" t="s">
+      <c r="I19" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="J19" s="18"/>
-      <c r="K19" s="18"/>
+      <c r="J19" s="19"/>
+      <c r="K19" s="19"/>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="I20" s="8"/>
@@ -12656,11 +12674,11 @@
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A22" s="19" t="s">
+      <c r="A22" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
       <c r="I22" s="1" t="s">
         <v>6</v>
       </c>
@@ -12980,11 +12998,11 @@
       </c>
     </row>
     <row r="38" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I38" s="18" t="s">
+      <c r="I38" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="J38" s="18"/>
-      <c r="K38" s="18"/>
+      <c r="J38" s="19"/>
+      <c r="K38" s="19"/>
     </row>
     <row r="39" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I39" s="8"/>
@@ -13281,11 +13299,11 @@
       </c>
     </row>
     <row r="56" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I56" s="18" t="s">
+      <c r="I56" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="J56" s="18"/>
-      <c r="K56" s="18"/>
+      <c r="J56" s="19"/>
+      <c r="K56" s="19"/>
     </row>
     <row r="57" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I57" s="8"/>
@@ -13600,11 +13618,11 @@
       </c>
     </row>
     <row r="75" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I75" s="18" t="s">
+      <c r="I75" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="J75" s="18"/>
-      <c r="K75" s="18"/>
+      <c r="J75" s="19"/>
+      <c r="K75" s="19"/>
     </row>
     <row r="76" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I76" s="8"/>
@@ -13779,7 +13797,7 @@
         <v>49</v>
       </c>
       <c r="N88" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="89" spans="9:15" x14ac:dyDescent="0.25">
@@ -13881,11 +13899,11 @@
       </c>
     </row>
     <row r="95" spans="9:15" x14ac:dyDescent="0.25">
-      <c r="I95" s="20" t="s">
+      <c r="I95" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="J95" s="20"/>
-      <c r="K95" s="20"/>
+      <c r="J95" s="18"/>
+      <c r="K95" s="18"/>
     </row>
     <row r="96" spans="9:15" x14ac:dyDescent="0.25">
       <c r="J96" s="1" t="s">
@@ -14000,12 +14018,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="I86:O86"/>
-    <mergeCell ref="I87:O87"/>
-    <mergeCell ref="I95:K95"/>
-    <mergeCell ref="I66:O66"/>
-    <mergeCell ref="I67:O67"/>
-    <mergeCell ref="I75:K75"/>
     <mergeCell ref="I56:K56"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A22:C22"/>
@@ -14019,6 +14031,12 @@
     <mergeCell ref="I38:K38"/>
     <mergeCell ref="I47:O47"/>
     <mergeCell ref="I48:O48"/>
+    <mergeCell ref="I86:O86"/>
+    <mergeCell ref="I87:O87"/>
+    <mergeCell ref="I95:K95"/>
+    <mergeCell ref="I66:O66"/>
+    <mergeCell ref="I67:O67"/>
+    <mergeCell ref="I75:K75"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Experiments data/K Size/K_Size_Email_Graph.xlsx
+++ b/Experiments data/K Size/K_Size_Email_Graph.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fengw\OneDrive\Documents\GitHub\KaMinPar_Java\Experiments data\K Size\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C114C28C-25A1-45BE-9D63-95858797BEA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13086B56-E227-44C8-9029-FCFA40A3FAC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-210" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Edge Cuts" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="50">
   <si>
     <t>Proposed w/PRRP w/o ILP</t>
   </si>
@@ -366,14 +366,14 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -11208,7 +11208,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:Q58"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24.28515625" bestFit="1" customWidth="1"/>
@@ -11997,7 +11997,7 @@
         <v>1.3620000000000001</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="17" t="s">
         <v>32</v>
       </c>
@@ -12008,7 +12008,7 @@
       <c r="F53" s="17"/>
       <c r="G53" s="17"/>
     </row>
-    <row r="54" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="B54" s="1" t="s">
         <v>10</v>
@@ -12034,8 +12034,21 @@
       <c r="I54" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="M54" s="2"/>
+      <c r="N54" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="O54" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P54" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q54" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>2</v>
       </c>
@@ -12071,8 +12084,23 @@
         <f>AVERAGE(I4:I8)</f>
         <v>0.6624000000000001</v>
       </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="M55" s="1">
+        <v>2</v>
+      </c>
+      <c r="N55">
+        <v>0.52259999999999995</v>
+      </c>
+      <c r="O55">
+        <v>0.46800000000000008</v>
+      </c>
+      <c r="P55">
+        <v>0.63260000000000005</v>
+      </c>
+      <c r="Q55">
+        <v>0.6624000000000001</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>4</v>
       </c>
@@ -12108,8 +12136,23 @@
         <f>AVERAGE(I14:I18)</f>
         <v>0.8256</v>
       </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="M56" s="1">
+        <v>4</v>
+      </c>
+      <c r="N56">
+        <v>0.63960000000000006</v>
+      </c>
+      <c r="O56">
+        <v>0.80920000000000003</v>
+      </c>
+      <c r="P56">
+        <v>0.85180000000000011</v>
+      </c>
+      <c r="Q56">
+        <v>0.8256</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>8</v>
       </c>
@@ -12145,8 +12188,23 @@
         <f>AVERAGE(I24:I28)</f>
         <v>1.1626000000000001</v>
       </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="M57" s="1">
+        <v>8</v>
+      </c>
+      <c r="N57">
+        <v>0.76340000000000008</v>
+      </c>
+      <c r="O57">
+        <v>1.0364</v>
+      </c>
+      <c r="P57">
+        <v>1.0902000000000001</v>
+      </c>
+      <c r="Q57">
+        <v>1.1626000000000001</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>16</v>
       </c>
@@ -12180,6 +12238,21 @@
       </c>
       <c r="I58">
         <f>AVERAGE(I35:I39)</f>
+        <v>1.3073999999999999</v>
+      </c>
+      <c r="M58" s="1">
+        <v>16</v>
+      </c>
+      <c r="N58">
+        <v>1.1254</v>
+      </c>
+      <c r="O58">
+        <v>1.5226</v>
+      </c>
+      <c r="P58">
+        <v>1.2802</v>
+      </c>
+      <c r="Q58">
         <v>1.3073999999999999</v>
       </c>
     </row>
@@ -12484,11 +12557,11 @@
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="I11" s="19" t="s">
+      <c r="I11" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="J11" s="19"/>
-      <c r="K11" s="19"/>
+      <c r="J11" s="20"/>
+      <c r="K11" s="20"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="J12" s="1" t="s">
@@ -12499,16 +12572,16 @@
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19" t="s">
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
       <c r="I13" s="1" t="s">
         <v>5</v>
       </c>
@@ -12617,11 +12690,11 @@
       <c r="C19" s="4">
         <v>1</v>
       </c>
-      <c r="I19" s="18" t="s">
+      <c r="I19" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="J19" s="18"/>
-      <c r="K19" s="18"/>
+      <c r="J19" s="19"/>
+      <c r="K19" s="19"/>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="I20" s="8"/>
@@ -12656,11 +12729,11 @@
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A22" s="19" t="s">
+      <c r="A22" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
       <c r="I22" s="1" t="s">
         <v>6</v>
       </c>
@@ -12980,11 +13053,11 @@
       </c>
     </row>
     <row r="38" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I38" s="18" t="s">
+      <c r="I38" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="J38" s="18"/>
-      <c r="K38" s="18"/>
+      <c r="J38" s="19"/>
+      <c r="K38" s="19"/>
     </row>
     <row r="39" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I39" s="8"/>
@@ -13281,11 +13354,11 @@
       </c>
     </row>
     <row r="56" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I56" s="18" t="s">
+      <c r="I56" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="J56" s="18"/>
-      <c r="K56" s="18"/>
+      <c r="J56" s="19"/>
+      <c r="K56" s="19"/>
     </row>
     <row r="57" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I57" s="8"/>
@@ -13600,11 +13673,11 @@
       </c>
     </row>
     <row r="75" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I75" s="18" t="s">
+      <c r="I75" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="J75" s="18"/>
-      <c r="K75" s="18"/>
+      <c r="J75" s="19"/>
+      <c r="K75" s="19"/>
     </row>
     <row r="76" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I76" s="8"/>
@@ -13881,11 +13954,11 @@
       </c>
     </row>
     <row r="95" spans="9:15" x14ac:dyDescent="0.25">
-      <c r="I95" s="20" t="s">
+      <c r="I95" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="J95" s="20"/>
-      <c r="K95" s="20"/>
+      <c r="J95" s="18"/>
+      <c r="K95" s="18"/>
     </row>
     <row r="96" spans="9:15" x14ac:dyDescent="0.25">
       <c r="J96" s="1" t="s">
@@ -14000,12 +14073,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="I86:O86"/>
-    <mergeCell ref="I87:O87"/>
-    <mergeCell ref="I95:K95"/>
-    <mergeCell ref="I66:O66"/>
-    <mergeCell ref="I67:O67"/>
-    <mergeCell ref="I75:K75"/>
     <mergeCell ref="I56:K56"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A22:C22"/>
@@ -14019,6 +14086,12 @@
     <mergeCell ref="I38:K38"/>
     <mergeCell ref="I47:O47"/>
     <mergeCell ref="I48:O48"/>
+    <mergeCell ref="I86:O86"/>
+    <mergeCell ref="I87:O87"/>
+    <mergeCell ref="I95:K95"/>
+    <mergeCell ref="I66:O66"/>
+    <mergeCell ref="I67:O67"/>
+    <mergeCell ref="I75:K75"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
